--- a/public/exports-from-60/29189501.xlsx
+++ b/public/exports-from-60/29189501.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158100</t>
+          <t xml:space="preserve">311158150</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158108</t>
+          <t xml:space="preserve">311158156</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -12139,12 +12139,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299905</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299908</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299910</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M164" t="inlineStr">

--- a/public/exports-from-60/29189501.xlsx
+++ b/public/exports-from-60/29189501.xlsx
@@ -4264,12 +4264,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158150</t>
+          <t xml:space="preserve">311158100</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311158156</t>
+          <t xml:space="preserve">311158108</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Erik Møllers Tegnestue</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299905</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299908</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299910</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
